--- a/artfynd/A 46629-2024 artfynd.xlsx
+++ b/artfynd/A 46629-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66589903</v>
+        <v>86917507</v>
       </c>
       <c r="B2" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45042</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220204</v>
+        <v>201164</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Zygaena filipendulae</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,30 +708,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>450 m V Fyrbo, Upl</t>
+          <t>Väg mot Vattmyren glänta, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>674529.2414496507</v>
+        <v>674541</v>
       </c>
       <c r="R2" t="n">
-        <v>6675606.373342839</v>
+        <v>6675652</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,27 +753,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-07-06</t>
+          <t>2020-07-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-07-06</t>
+          <t>2020-07-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Växer i vägkanten.</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,21 +777,143 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Susanne Ahlman</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Susanne Ahlman</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Kampanj Bastardsvärmare</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>66589903</v>
+      </c>
+      <c r="B3" t="n">
+        <v>109815</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>450 m V Fyrbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>674529</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6675606</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Skäfthammar</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2017-07-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2017-07-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Växer i vägkanten.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Thorleif Joelson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Thorleif Joelson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46629-2024 artfynd.xlsx
+++ b/artfynd/A 46629-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Kampanj Bastardsvärmare</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86917507</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,8 +924,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66589903</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>